--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3253" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3253" uniqueCount="639">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1570,10 +1570,6 @@
     <t>Observation.bodySite.extension.id</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Observation.bodySite.extension:precisionTopographique.extension</t>
   </si>
   <si>
@@ -1620,14 +1616,10 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Observation.bodySite.coding</t>
@@ -8928,7 +8920,7 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>168</v>
@@ -8994,7 +8986,7 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>82</v>
@@ -9020,10 +9012,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9049,10 +9041,10 @@
         <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9138,10 +9130,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9167,13 +9159,13 @@
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9181,49 +9173,49 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>93</v>
@@ -9258,10 +9250,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9284,13 +9276,13 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9341,7 +9333,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9350,7 +9342,7 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
@@ -9376,10 +9368,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9498,10 +9490,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9620,10 +9612,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9649,16 +9641,16 @@
         <v>191</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9686,10 +9678,10 @@
         <v>370</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9707,7 +9699,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9728,10 +9720,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9742,10 +9734,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9768,16 +9760,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9827,7 +9819,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9845,27 +9837,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>536</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9888,16 +9880,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9947,7 +9939,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9965,27 +9957,27 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>545</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10008,19 +10000,19 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10069,7 +10061,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10081,19 +10073,19 @@
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10104,10 +10096,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10222,10 +10214,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10342,14 +10334,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10371,10 +10363,10 @@
         <v>139</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>142</v>
@@ -10429,7 +10421,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10464,10 +10456,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10490,13 +10482,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10547,7 +10539,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10556,7 +10548,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10568,10 +10560,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10582,10 +10574,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10608,13 +10600,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10665,7 +10657,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10674,7 +10666,7 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10686,10 +10678,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10700,10 +10692,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10729,16 +10721,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10766,10 +10758,10 @@
         <v>117</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10787,7 +10779,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10805,10 +10797,10 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>469</v>
@@ -10822,10 +10814,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10851,16 +10843,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10888,10 +10880,10 @@
         <v>370</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10909,7 +10901,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10927,10 +10919,10 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>469</v>
@@ -10944,10 +10936,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10970,17 +10962,17 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11029,7 +11021,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11053,7 +11045,7 @@
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11064,10 +11056,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11093,10 +11085,10 @@
         <v>167</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11147,7 +11139,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11168,10 +11160,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11182,10 +11174,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11208,16 +11200,16 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11267,7 +11259,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11288,10 +11280,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11302,10 +11294,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11328,16 +11320,16 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11387,7 +11379,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11408,10 +11400,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11422,10 +11414,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11448,19 +11440,19 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11509,7 +11501,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11530,10 +11522,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11544,10 +11536,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11662,10 +11654,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11782,14 +11774,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11811,10 +11803,10 @@
         <v>139</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>142</v>
@@ -11869,7 +11861,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11904,10 +11896,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11933,13 +11925,13 @@
         <v>191</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="O80" t="s" s="2">
         <v>368</v>
@@ -11971,7 +11963,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -11989,7 +11981,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>93</v>
@@ -12007,7 +11999,7 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>375</v>
@@ -12024,10 +12016,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12050,16 +12042,16 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>442</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>444</v>
@@ -12111,7 +12103,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12129,7 +12121,7 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>447</v>
@@ -12146,10 +12138,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12175,13 +12167,13 @@
         <v>191</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="O82" t="s" s="2">
         <v>454</v>
@@ -12233,7 +12225,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12268,10 +12260,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12355,7 +12347,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12390,10 +12382,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12419,16 +12411,16 @@
         <v>83</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12477,7 +12469,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12498,10 +12490,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
